--- a/documentacion/VIVEPIOLA_Registro_Copropietarios.xlsx
+++ b/documentacion/VIVEPIOLA_Registro_Copropietarios.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -515,17 +515,13 @@
       </c>
       <c r="B1" s="2" t="inlineStr"/>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Una fila por PERSONA, no por departamento.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -533,12 +529,8 @@
           <t>Si un depto tiene propietario y arrendatario, van dos filas con la misma unidad.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -643,7 +635,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opcional. PERMANENTE (por defecto) o TRANSITORIO (hospedaje temporal)</t>
+          <t>Opcional. PERMANENTE (por defecto) o TRANSITORIO (hospedaje temporal, estadia corta). Marcar TRANSITORIO hace que la notificacion se copie al propietario.</t>
         </is>
       </c>
     </row>
@@ -655,14 +647,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opcional. CONYUGE, CONVIVIENTE_CIVIL o FAMILIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-    </row>
+          <t>Opcional. CONYUGE, CONVIVIENTE_CIVIL o FAMILIAR. Si ocupa por vinculo con el dueno, la notificacion tambien se le copia a el.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -677,7 +666,6 @@
           <t>El PROPIETARIO es el obligado al pago ante la comunidad.</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -685,7 +673,6 @@
           <t>Si multan al arrendatario, el cargo igual se emite a nombre del dueño de la unidad.</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -693,12 +680,8 @@
           <t>Por eso cada unidad deberia tener su propietario registrado.</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -743,17 +726,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>El sistema valida fila por fila: importa las correctas e informa cuales fallaron.</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -761,7 +740,48 @@
           <t>Puedes volver a subir el archivo corregido: las personas ya cargadas se actualizan.</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>A QUIEN LE LLEGA LA NOTIFICACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>La notificacion legal va al correo del infractor. Ademas se copia al propietario cuando:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - la persona es TRANSITORIO: puede haberse ido antes de que venza el plazo de descargo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - la persona ocupa por vinculo con el dueno (conyuge, conviviente civil, familiar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>En los demas casos no se copia a nadie mas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Por eso conviene llenar estas dos columnas: son las que definen a quien le llega.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/documentacion/VIVEPIOLA_Registro_Copropietarios.xlsx
+++ b/documentacion/VIVEPIOLA_Registro_Copropietarios.xlsx
@@ -515,13 +515,17 @@
       </c>
       <c r="B1" s="2" t="inlineStr"/>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Una fila por PERSONA, no por departamento.</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -529,8 +533,12 @@
           <t>Si un depto tiene propietario y arrendatario, van dos filas con la misma unidad.</t>
         </is>
       </c>
-    </row>
-    <row r="5"/>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+    </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -647,11 +655,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opcional. CONYUGE, CONVIVIENTE_CIVIL o FAMILIAR. Si ocupa por vinculo con el dueno, la notificacion tambien se le copia a el.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>Opcional. CONYUGE, CONVIVIENTE_CIVIL o FAMILIAR. Si ocupa por vinculo con el dueño, la notificacion tambien se le copia a el.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+    </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -666,6 +677,7 @@
           <t>El PROPIETARIO es el obligado al pago ante la comunidad.</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -673,6 +685,7 @@
           <t>Si multan al arrendatario, el cargo igual se emite a nombre del dueño de la unidad.</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -680,12 +693,16 @@
           <t>Por eso cada unidad deberia tener su propietario registrado.</t>
         </is>
       </c>
-    </row>
-    <row r="21"/>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+    </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ERRORES QUE RECHAZAN LA FILA</t>
+          <t>A QUIEN LE LLEGA LA NOTIFICACION</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
@@ -693,95 +710,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Correo vacio o mal escrito</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Sin correo no se puede notificar y la multa queda bloqueada</t>
-        </is>
-      </c>
+          <t>La notificacion legal va al correo del infractor. Ademas se copia al propietario cuando:</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rol_ocupacion fuera de la lista</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>En mayusculas y sin acentos</t>
-        </is>
-      </c>
+          <t xml:space="preserve">   - la persona es TRANSITORIO: puede haberse ido antes de que venza el plazo de descargo.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Falta nombre, cedula, domicilio o unidad</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Todos obligatorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+          <t xml:space="preserve">   - la persona ocupa por vinculo con el dueño (conyuge, conviviente civil, familiar).</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>En los demas casos no se copia a nadie mas.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>El sistema valida fila por fila: importa las correctas e informa cuales fallaron.</t>
-        </is>
-      </c>
+          <t>Por eso conviene llenar estas dos columnas: son las que definen a quien le llega.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Puedes volver a subir el archivo corregido: las personas ya cargadas se actualizan.</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ERRORES QUE RECHAZAN LA FILA</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>A QUIEN LE LLEGA LA NOTIFICACION</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Correo vacio o mal escrito</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sin correo no se puede notificar y la multa queda bloqueada</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>La notificacion legal va al correo del infractor. Ademas se copia al propietario cuando:</t>
+          <t>rol_ocupacion fuera de la lista</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>En mayusculas y sin acentos</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - la persona es TRANSITORIO: puede haberse ido antes de que venza el plazo de descargo.</t>
+          <t>Falta nombre, cedula, domicilio o unidad</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Todos obligatorios</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - la persona ocupa por vinculo con el dueno (conyuge, conviviente civil, familiar).</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>En los demas casos no se copia a nadie mas.</t>
-        </is>
-      </c>
+          <t>El sistema valida fila por fila: importa las correctas e informa cuales fallaron.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Por eso conviene llenar estas dos columnas: son las que definen a quien le llega.</t>
-        </is>
-      </c>
+          <t>Puedes volver a subir el archivo corregido: las personas ya cargadas se actualizan.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/documentacion/VIVEPIOLA_Registro_Copropietarios.xlsx
+++ b/documentacion/VIVEPIOLA_Registro_Copropietarios.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Copropietarios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Copropietarios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00111827"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006B7280"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,10 +64,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -137,6 +143,61 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>VIVEPIOLA</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Obligatorio. El departamento, casa o estacionamiento. Ej: Depto 302</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Obligatorio. Titulo con que ocupa la unidad. Elija de la lista.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Obligatorio. Nombre y apellidos de la persona.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Obligatorio. RUT con guion. Ej: 12.345.678-9</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Obligatorio. Direccion de la unidad.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Obligatorio. Es el canal legal de notificacion: sin correo valido la multa no se puede notificar.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Formato +569XXXXXXXX. Habilita el aviso por WhatsApp.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. PERMANENTE si no se indica. TRANSITORIO (estadia corta) hace que la notificacion se copie tambien al propietario.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Solo si ocupa por su vinculo con el dueño. En ese caso la notificacion tambien se le copia al propietario.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,6 +489,376 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>COMO LLENAR ESTA PLANILLA</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Los datos van en la otra hoja, la de abajo: "Registro Copropietarios".</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Una fila por PERSONA, no por departamento.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Si un depto tiene propietario y arrendatario, van dos filas con la misma unidad.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Encabezado oscuro = obligatorio. Encabezado gris = opcional.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Al pararse en una celda aparece la ayuda de esa columna.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rol_ocupacion, permanencia y vinculo_copropietario son listas desplegables:</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   elija el valor y no tendra que acordarse de escribirlo en mayusculas.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>COLUMNA</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>QUE VA / REGLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>unidad</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ej: Depto 302, Estacionamiento 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>rol_ocupacion</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Titulo con que ocupa: ARRENDATARIO, COMODATARIO, OCUPANTE, PROPIETARIO, USUFRUCTUARIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>nombre_completo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nombre y apellidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cedula_identidad</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RUT con guion. Ej: 12.345.678-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>domicilio</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Direccion de la unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>correo_electronico</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OBLIGATORIO: es el canal legal de notificacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>telefono</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Opcional. +569XXXXXXXX. Habilita el aviso por WhatsApp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>permanencia</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Opcional. PERMANENTE (por defecto) o TRANSITORIO (hospedaje temporal, estadia corta). Marcar TRANSITORIO hace que la notificacion se copie al propietario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>vinculo_copropietario</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Opcional. CONYUGE, CONVIVIENTE_CIVIL o FAMILIAR. Si ocupa por vinculo con el dueño, la notificacion tambien se le copia a el.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QUIEN PAGA</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>El PROPIETARIO es el obligado al pago ante la comunidad.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Si multan al arrendatario, el cargo igual se emite a nombre del dueño de la unidad.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Por eso cada unidad deberia tener su propietario registrado.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>A QUIEN LE LLEGA LA NOTIFICACION</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>La notificacion legal va al correo del infractor. Ademas se copia al propietario cuando:</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - la persona es TRANSITORIO: puede haberse ido antes de que venza el plazo de descargo.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - la persona ocupa por vinculo con el dueño (conyuge, conviviente civil, familiar).</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>En los demas casos no se copia a nadie mas.</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Por eso conviene llenar estas dos columnas: son las que definen a quien le llega.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ERRORES QUE RECHAZAN LA FILA</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Correo vacio o mal escrito</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sin correo no se puede notificar y la multa queda bloqueada</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>rol_ocupacion fuera de la lista</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>En mayusculas y sin acentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Falta nombre, cedula, domicilio o unidad</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Todos obligatorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>El sistema valida fila por fila: importa las correctas e informa cuales fallaron.</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Puedes volver a subir el archivo corregido: las personas ya cargadas se actualizan.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -443,379 +874,71 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>rol_ocupacion</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>nombre_completo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>cedula_identidad</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>domicilio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>correo_electronico</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>telefono</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>permanencia</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>vinculo_copropietario</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="9">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="unidad" prompt="Obligatorio. El departamento, casa o estacionamiento. Ej: Depto 302"/>
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Valor no valido" error="Use uno de estos valores: ARRENDATARIO, COMODATARIO, OCUPANTE, PROPIETARIO, USUFRUCTUARIO" promptTitle="rol_ocupacion" prompt="Titulo con que ocupa la unidad. Elija de la lista." type="list">
+      <formula1>"ARRENDATARIO,COMODATARIO,OCUPANTE,PROPIETARIO,USUFRUCTUARIO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="nombre_completo" prompt="Obligatorio. Nombre y apellidos de la persona."/>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="cedula_identidad" prompt="Obligatorio. RUT con guion. Ej: 12.345.678-9"/>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="domicilio" prompt="Obligatorio. Direccion de la unidad."/>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="correo_electronico" prompt="Obligatorio. Es el canal legal de notificacion: sin correo valido la multa no se puede notificar."/>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="telefono" prompt="Opcional. Formato +569XXXXXXXX. Habilita el aviso por WhatsApp."/>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Valor no valido" error="Use uno de estos valores: PERMANENTE, TRANSITORIO" promptTitle="permanencia" prompt="PERMANENTE si no se indica. TRANSITORIO (estadia corta) hace que la notificacion se copie tambien al propietario." type="list">
+      <formula1>"PERMANENTE,TRANSITORIO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Valor no valido" error="Use uno de estos valores: CONVIVIENTE_CIVIL, CONYUGE, FAMILIAR" promptTitle="vinculo_copropietario" prompt="Solo si ocupa por su vinculo con el dueño. En ese caso la notificacion tambien se le copia al propietario." type="list">
+      <formula1>"CONVIVIENTE_CIVIL,CONYUGE,FAMILIAR"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>COMO LLENAR ESTA PLANILLA</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Una fila por PERSONA, no por departamento.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Si un depto tiene propietario y arrendatario, van dos filas con la misma unidad.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>COLUMNA</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>QUE VA / REGLAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>unidad</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ej: Depto 302, Estacionamiento 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>rol_ocupacion</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Titulo con que ocupa: ARRENDATARIO, COMODATARIO, OCUPANTE, PROPIETARIO, USUFRUCTUARIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>nombre_completo</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Nombre y apellidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cedula_identidad</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>RUT con guion. Ej: 12.345.678-9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>domicilio</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Direccion de la unidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>correo_electronico</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>OBLIGATORIO: es el canal legal de notificacion</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>telefono</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Opcional. +569XXXXXXXX. Habilita el aviso por WhatsApp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>permanencia</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Opcional. PERMANENTE (por defecto) o TRANSITORIO (hospedaje temporal, estadia corta). Marcar TRANSITORIO hace que la notificacion se copie al propietario.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>vinculo_copropietario</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Opcional. CONYUGE, CONVIVIENTE_CIVIL o FAMILIAR. Si ocupa por vinculo con el dueño, la notificacion tambien se le copia a el.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>QUIEN PAGA</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>El PROPIETARIO es el obligado al pago ante la comunidad.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Si multan al arrendatario, el cargo igual se emite a nombre del dueño de la unidad.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Por eso cada unidad deberia tener su propietario registrado.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>A QUIEN LE LLEGA LA NOTIFICACION</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>La notificacion legal va al correo del infractor. Ademas se copia al propietario cuando:</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - la persona es TRANSITORIO: puede haberse ido antes de que venza el plazo de descargo.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - la persona ocupa por vinculo con el dueño (conyuge, conviviente civil, familiar).</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>En los demas casos no se copia a nadie mas.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Por eso conviene llenar estas dos columnas: son las que definen a quien le llega.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ERRORES QUE RECHAZAN LA FILA</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Correo vacio o mal escrito</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Sin correo no se puede notificar y la multa queda bloqueada</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>rol_ocupacion fuera de la lista</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>En mayusculas y sin acentos</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Falta nombre, cedula, domicilio o unidad</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Todos obligatorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>El sistema valida fila por fila: importa las correctas e informa cuales fallaron.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Puedes volver a subir el archivo corregido: las personas ya cargadas se actualizan.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/documentacion/VIVEPIOLA_Registro_Copropietarios.xlsx
+++ b/documentacion/VIVEPIOLA_Registro_Copropietarios.xlsx
@@ -196,6 +196,11 @@
         <t>Opcional. Solo si ocupa por su vinculo con el dueño. En ese caso la notificacion tambien se le copia al propietario.</t>
       </text>
     </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Solo si corresponde: FALLECIDO, DISCAPACIDAD o REQUIERE_APOYO. Detiene el cobro automatico para que el Comite revise el caso antes de cobrarlo.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -489,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -555,7 +560,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rol_ocupacion, permanencia y vinculo_copropietario son listas desplegables:</t>
+          <t>rol_ocupacion, permanencia, vinculo y condicion son listas desplegables:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -693,29 +698,33 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>condicion_especial</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Opcional. FALLECIDO, DISCAPACIDAD o REQUIERE_APOYO. Detiene el cobro automatico para que el Comite confirme antes de cobrar.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>QUIEN PAGA</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>El PROPIETARIO es el obligado al pago ante la comunidad.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" s="1" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Si multan al arrendatario, el cargo igual se emite a nombre del dueño de la unidad.</t>
+          <t>El PROPIETARIO es el obligado al pago ante la comunidad.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -723,35 +732,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Si multan al arrendatario, el cargo igual se emite a nombre del dueño de la unidad.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Por eso cada unidad deberia tener su propietario registrado.</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>A QUIEN LE LLEGA LA NOTIFICACION</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>La notificacion legal va al correo del infractor. Ademas se copia al propietario cuando:</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" s="1" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - la persona es TRANSITORIO: puede haberse ido antes de que venza el plazo de descargo.</t>
+          <t>La notificacion legal va al correo del infractor. Ademas se copia al propietario cuando:</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -759,7 +768,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - la persona ocupa por vinculo con el dueño (conyuge, conviviente civil, familiar).</t>
+          <t xml:space="preserve">   - la persona es TRANSITORIO: puede haberse ido antes de que venza el plazo de descargo.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -767,7 +776,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>En los demas casos no se copia a nadie mas.</t>
+          <t xml:space="preserve">   - la persona ocupa por vinculo con el dueño (conyuge, conviviente civil, familiar).</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -775,78 +784,86 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>En los demas casos no se copia a nadie mas.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Por eso conviene llenar estas dos columnas: son las que definen a quien le llega.</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>ERRORES QUE RECHAZAN LA FILA</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Correo vacio o mal escrito</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Sin correo no se puede notificar y la multa queda bloqueada</t>
-        </is>
-      </c>
+      <c r="B36" s="1" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rol_ocupacion fuera de la lista</t>
+          <t>Correo vacio o mal escrito</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>En mayusculas y sin acentos</t>
+          <t>Sin correo no se puede notificar y la multa queda bloqueada</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>rol_ocupacion fuera de la lista</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>En mayusculas y sin acentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Falta nombre, cedula, domicilio o unidad</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Todos obligatorios</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-    </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>El sistema valida fila por fila: importa las correctas e informa cuales fallaron.</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>El sistema valida fila por fila: importa las correctas e informa cuales fallaron.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Puedes volver a subir el archivo corregido: las personas ya cargadas se actualizan.</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -859,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -871,6 +888,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -919,9 +937,14 @@
           <t>vinculo_copropietario</t>
         </is>
       </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>condicion_especial</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="10">
     <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="unidad" prompt="Obligatorio. El departamento, casa o estacionamiento. Ej: Depto 302"/>
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Valor no valido" error="Use uno de estos valores: ARRENDATARIO, COMODATARIO, OCUPANTE, PROPIETARIO, USUFRUCTUARIO" promptTitle="rol_ocupacion" prompt="Titulo con que ocupa la unidad. Elija de la lista." type="list">
       <formula1>"ARRENDATARIO,COMODATARIO,OCUPANTE,PROPIETARIO,USUFRUCTUARIO"</formula1>
@@ -937,6 +960,9 @@
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Valor no valido" error="Use uno de estos valores: CONVIVIENTE_CIVIL, CONYUGE, FAMILIAR" promptTitle="vinculo_copropietario" prompt="Solo si ocupa por su vinculo con el dueño. En ese caso la notificacion tambien se le copia al propietario." type="list">
       <formula1>"CONVIVIENTE_CIVIL,CONYUGE,FAMILIAR"</formula1>
     </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Valor no valido" error="Use uno de estos valores: DISCAPACIDAD, FALLECIDO, REQUIERE_APOYO" promptTitle="condicion_especial" prompt="Solo si corresponde: FALLECIDO, DISCAPACIDAD o REQUIERE_APOYO. Detiene el cobro automatico para que el Comite revise el caso antes de cobrarlo." type="list">
+      <formula1>"DISCAPACIDAD,FALLECIDO,REQUIERE_APOYO"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
